--- a/Employee_Reports_wi48/Jake Alinabon Salibay Q0554.xlsx
+++ b/Employee_Reports_wi48/Jake Alinabon Salibay Q0554.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-58</v>
+        <v>-61</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-68</v>
+        <v>-71</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-52</v>
+        <v>-55</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-33</v>
+        <v>-36</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-54</v>
+        <v>-57</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-89</v>
+        <v>-92</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-279</v>
+        <v>-282</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-273</v>
+        <v>-276</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-642</v>
+        <v>-645</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-95</v>
+        <v>-98</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1435,9 +1435,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>10-Apr-2025</t>
@@ -1449,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-94</v>
+        <v>-97</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1596,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1645,11 +1657,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1682,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1719,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1768,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1817,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
